--- a/input/mapping/079. OCB_GOLD_TCKH_V_DATE_OF_WORK_HOP.xlsx
+++ b/input/mapping/079. OCB_GOLD_TCKH_V_DATE_OF_WORK_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1797" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFBB1F2D-0102-4143-9649-6636FC06429F}"/>
+  <xr:revisionPtr revIDLastSave="1802" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7703557-A026-4074-A63A-7CC71C5943BF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="1" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
     <sheet name="FTP_CONTRACT" sheetId="30" state="hidden" r:id="rId13"/>
     <sheet name="V_FTP_INTEREST_RATE_NIM_ON" sheetId="15" state="hidden" r:id="rId14"/>
     <sheet name="FTP_RATE_LIST_HIST" sheetId="17" state="hidden" r:id="rId15"/>
-    <sheet name="V_DATE_OF_WORK" sheetId="32" r:id="rId16"/>
+    <sheet name="V_DATE_OF_WORK (2)" sheetId="33" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2112" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2170" uniqueCount="467">
   <si>
     <t>V_DATE_OF_WORK —  Data Lineage Summary</t>
   </si>
@@ -125,41 +125,40 @@
     <t>code mới</t>
   </si>
   <si>
-    <t>USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
--- =============================================================================
--- V_DATE_OF_WORK
--- Nguồn: calendar (Silver / business_vault) - chỉ lấy ngày làm việc (BSN_DAY_F = 1)
--- Nguồn calendar ở catalog :cleaned (khác default) -&gt; giữ IDENTIFIER
--- =============================================================================
 CREATE OR REPLACE VIEW V_DATE_OF_WORK AS
 SELECT
-      D.MSR_PRD_ID AS CDR_DT_ID
-    , D.MSR_PRD_ID
-    , D.CDR_YR
-    , D.CDR_QTR
-    , D.CDR_MO
-    , D.WK_OF_FSC_YR
-    , D.FSC_YR
-    , D.FSC_QTR
-    , D.FSC_MO
-    , D.WK_OF_CDR_YR
-    , D.DAY_OF_CDR_YR
-    , D.DAY_OF_WK
-    , D.DAY_CDR_MO
-    , D.END_OF_MO_DT
-    , D.PBLC_HOL_F
-    , D.BSN_DAY_F
-    , D.TM_PRD_TP_ID
-    , D.DATA_DT
-    , D.LAST_BSN_DAY_F
-    , DATEDIFF(
-          D.END_OF_MO_DT,
-          TO_DATE(CAST(D.MSR_PRD_ID AS STRING), 'yyyyMMdd')
-      ) + D.DAY_CDR_MO AS NUM_DAY_OF_MO_DT
-FROM IDENTIFIER(:cleaned || '.business_vault.calendar') D
-WHERE D.BSN_DAY_F = 1
-;</t>
+    c.msr_prd_id,
+    c.msr_prd_id                                                AS cdr_dt_id,
+    c.cdr_yr,
+    c.cdr_qtr,
+    CAST(SUBSTR(CAST(c.msr_prd_id AS STRING), 5, 2) AS INT)    AS cdr_mo,
+    WEEKOFYEAR(c.msr_prd_dt)                                    AS wk_of_fsc_yr,
+    c.cdr_yr                                                    AS fsc_yr,
+    c.cdr_qtr                                                   AS fsc_qtr,
+    CAST(SUBSTR(CAST(c.msr_prd_id AS STRING), 5, 2) AS INT)    AS fsc_mo,
+    WEEKOFYEAR(c.msr_prd_dt)                                    AS wk_of_cdr_yr,
+    DAYOFYEAR(c.msr_prd_dt)                                     AS day_of_cdr_yr,
+    c.day_of_wk,
+    DAY(c.msr_prd_dt)                                           AS day_cdr_mo,
+    LAST_DAY(c.msr_prd_dt)                                      AS end_of_mo_dt,
+    c.pblc_hol_f,
+    c.bsn_day_f,
+    CAST(1 AS INT)                                              AS tm_prd_tp_id,
+    c.msr_prd_dt                                                AS data_dt,
+    c.last_bsn_day_f,
+    DAY(LAST_DAY(c.msr_prd_dt))                                 AS num_day_of_mo_dt,
+    c.next_wk_id,
+    c.last_wk_id,
+    c.next_wk_dt,
+    c.last_wk_dt,
+    c.is_w_bom,
+    c.is_w_eom,
+    c.is_w_boy,
+    c.is_w_eoy
+FROM IDENTIFIER(:cleaned || '.business_vault.calendar') c
+</t>
   </si>
   <si>
     <t>JOIN SCHEMA</t>
@@ -1403,11 +1402,10 @@
   </si>
   <si>
     <t>ocb_datavault_dev_cleaned.business_vault.calendar
-(:cleaned .business_vault.calendar — thay MSR_PRD/OCBDW2.MSR_PRD)</t>
-  </si>
-  <si>
-    <t>WHERE D.BSN_DAY_F = 1
-— Chỉ lấy ngày làm việc (Business Day Flag = 1)</t>
+(:cleaned .business_vault.calendar) — alias c</t>
+  </si>
+  <si>
+    <t>Không còn WHERE lọc BSN_DAY_F = 1 — script mới SELECT toàn bộ các dòng của calendar (không chỉ ngày làm việc).</t>
   </si>
   <si>
     <t>Target View</t>
@@ -1416,119 +1414,192 @@
     <t>V_DATE_OF_WORK</t>
   </si>
   <si>
-    <t>D.MSR_PRD_ID AS CDR_DT_ID  — alias</t>
+    <t>c.msr_prd_id AS cdr_dt_id — alias</t>
   </si>
   <si>
     <t>MSR_PRD_ID</t>
   </si>
   <si>
+    <t>c.msr_prd_id</t>
+  </si>
+  <si>
     <t>CDR_YR</t>
   </si>
   <si>
-    <t>D.CDR_YR</t>
+    <t>c.cdr_yr</t>
   </si>
   <si>
     <t>CDR_QTR</t>
   </si>
   <si>
-    <t>D.CDR_QTR</t>
+    <t>c.cdr_qtr</t>
   </si>
   <si>
     <t>CDR_MO</t>
   </si>
   <si>
-    <t>D.CDR_MO</t>
+    <t>CAST(SUBSTR(CAST(c.msr_prd_id AS STRING),5,2) AS INT)
+— THAY ĐỔI: trước lấy D.CDR_MO trực tiếp, giờ tính từ msr_prd_id (ký tự 5-6 = tháng)</t>
   </si>
   <si>
     <t>WK_OF_FSC_YR</t>
   </si>
   <si>
-    <t>D.WK_OF_FSC_YR</t>
+    <t>WEEKOFYEAR(c.msr_prd_dt)
+— THAY ĐỔI: trước lấy D.WK_OF_FSC_YR, giờ tính từ msr_prd_dt</t>
   </si>
   <si>
     <t>FSC_YR</t>
   </si>
   <si>
-    <t>D.FSC_YR</t>
+    <t>c.cdr_yr AS fsc_yr
+— THAY ĐỔI: lấy từ cdr_yr thay vì field fsc_yr riêng</t>
   </si>
   <si>
     <t>FSC_QTR</t>
   </si>
   <si>
-    <t>D.FSC_QTR</t>
+    <t>c.cdr_qtr AS fsc_qtr
+— THAY ĐỔI: lấy từ cdr_qtr thay vì field fsc_qtr riêng</t>
   </si>
   <si>
     <t>FSC_MO</t>
   </si>
   <si>
-    <t>D.FSC_MO</t>
+    <t>CAST(SUBSTR(CAST(c.msr_prd_id AS STRING),5,2) AS INT)
+— THAY ĐỔI: cùng công thức với CDR_MO, không lấy field fsc_mo riêng</t>
   </si>
   <si>
     <t>WK_OF_CDR_YR</t>
   </si>
   <si>
-    <t>D.WK_OF_CDR_YR</t>
+    <t>WEEKOFYEAR(c.msr_prd_dt)
+— THAY ĐỔI: tính từ msr_prd_dt thay vì lấy field có sẵn</t>
   </si>
   <si>
     <t>DAY_OF_CDR_YR</t>
   </si>
   <si>
-    <t>D.DAY_OF_CDR_YR</t>
+    <t>DAYOFYEAR(c.msr_prd_dt)
+— THAY ĐỔI: tính từ msr_prd_dt thay vì lấy field có sẵn</t>
   </si>
   <si>
     <t>DAY_OF_WK</t>
   </si>
   <si>
-    <t>D.DAY_OF_WK</t>
+    <t>c.day_of_wk</t>
   </si>
   <si>
     <t>DAY_CDR_MO</t>
   </si>
   <si>
-    <t>D.DAY_CDR_MO</t>
+    <t>DAY(c.msr_prd_dt)
+— THAY ĐỔI: tính từ msr_prd_dt thay vì lấy field có sẵn</t>
   </si>
   <si>
     <t>END_OF_MO_DT</t>
   </si>
   <si>
-    <t>D.END_OF_MO_DT</t>
+    <t>LAST_DAY(c.msr_prd_dt)
+— THAY ĐỔI: tính từ msr_prd_dt thay vì lấy field có sẵn</t>
   </si>
   <si>
     <t>PBLC_HOL_F</t>
   </si>
   <si>
-    <t>D.PBLC_HOL_F</t>
+    <t>c.pblc_hol_f</t>
   </si>
   <si>
     <t>BSN_DAY_F</t>
   </si>
   <si>
-    <t>D.BSN_DAY_F</t>
+    <t>c.bsn_day_f</t>
   </si>
   <si>
     <t>TM_PRD_TP_ID</t>
   </si>
   <si>
-    <t>D.TM_PRD_TP_ID</t>
-  </si>
-  <si>
-    <t>D.DATA_DT</t>
+    <t>CAST(1 AS INT) AS tm_prd_tp_id
+— THAY ĐỔI: hardcode = 1, trước lấy từ field TM_PRD_TP_ID của nguồn</t>
+  </si>
+  <si>
+    <t>c.msr_prd_dt AS data_dt
+— THAY ĐỔI: nguồn là field msr_prd_dt (không phải data_dt) của calendar</t>
   </si>
   <si>
     <t>LAST_BSN_DAY_F</t>
   </si>
   <si>
-    <t>D.LAST_BSN_DAY_F</t>
+    <t>c.last_bsn_day_f</t>
   </si>
   <si>
     <t>NUM_DAY_OF_MO_DT</t>
   </si>
   <si>
-    <t>DATEDIFF(D.END_OF_MO_DT,
-  TO_DATE(CAST(D.MSR_PRD_ID AS STRING),'yyyyMMdd'))
-+ D.DAY_CDR_MO
-— NZ: DAYS(END_OF_MO_DT) - DAYS(TO_DATE(MSR_PRD_ID)) + DAY_CDR_MO
-— Spark SQL: DATEDIFF(end, start) thay DAYS(d1)-DAYS(d2)</t>
+    <t>DAY(LAST_DAY(c.msr_prd_dt))
+— THAY ĐỔI HOÀN TOÀN: trước = DATEDIFF(END_OF_MO_DT, TO_DATE(MSR_PRD_ID)) + DAY_CDR_MO; giờ = số ngày của tháng (DAY của LAST_DAY)</t>
+  </si>
+  <si>
+    <t>NEXT_WK_ID</t>
+  </si>
+  <si>
+    <t>new column</t>
+  </si>
+  <si>
+    <t>c.next_wk_id
+— MỚI: cột bổ sung trong script mới, không có trong version cũ</t>
+  </si>
+  <si>
+    <t>LAST_WK_ID</t>
+  </si>
+  <si>
+    <t>c.last_wk_id
+— MỚI: cột bổ sung trong script mới, không có trong version cũ</t>
+  </si>
+  <si>
+    <t>NEXT_WK_DT</t>
+  </si>
+  <si>
+    <t>c.next_wk_dt
+— MỚI: cột bổ sung trong script mới, không có trong version cũ</t>
+  </si>
+  <si>
+    <t>LAST_WK_DT</t>
+  </si>
+  <si>
+    <t>c.last_wk_dt
+— MỚI: cột bổ sung trong script mới, không có trong version cũ</t>
+  </si>
+  <si>
+    <t>IS_W_BOM</t>
+  </si>
+  <si>
+    <t>BOOLEAN</t>
+  </si>
+  <si>
+    <t>c.is_w_bom
+— MỚI: cột bổ sung trong script mới, không có trong version cũ</t>
+  </si>
+  <si>
+    <t>IS_W_EOM</t>
+  </si>
+  <si>
+    <t>c.is_w_eom
+— MỚI: cột bổ sung trong script mới, không có trong version cũ</t>
+  </si>
+  <si>
+    <t>IS_W_BOY</t>
+  </si>
+  <si>
+    <t>c.is_w_boy
+— MỚI: cột bổ sung trong script mới, không có trong version cũ</t>
+  </si>
+  <si>
+    <t>IS_W_EOY</t>
+  </si>
+  <si>
+    <t>c.is_w_eoy
+— MỚI: cột bổ sung trong script mới, không có trong version cũ</t>
   </si>
 </sst>
 </file>
@@ -2350,7 +2421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2749,8 +2820,215 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2761,218 +3039,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3359,12 +3427,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="151" t="s">
+      <c r="A1" s="147" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="152"/>
-      <c r="C1" s="152"/>
-      <c r="D1" s="152"/>
+      <c r="B1" s="148"/>
+      <c r="C1" s="148"/>
+      <c r="D1" s="148"/>
       <c r="E1" s="120"/>
       <c r="F1" s="120"/>
       <c r="G1" s="120"/>
@@ -3411,14 +3479,14 @@
       <c r="AV1" s="39"/>
     </row>
     <row r="2" spans="1:48">
-      <c r="A2" s="153" t="s">
+      <c r="A2" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="156" t="s">
+      <c r="B2" s="149"/>
+      <c r="C2" s="152" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="158" t="s">
+      <c r="D2" s="154" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="123"/>
@@ -3428,10 +3496,10 @@
       <c r="I2" s="123"/>
     </row>
     <row r="3" spans="1:48">
-      <c r="A3" s="154"/>
-      <c r="B3" s="154"/>
-      <c r="C3" s="157"/>
-      <c r="D3" s="159"/>
+      <c r="A3" s="150"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="153"/>
+      <c r="D3" s="155"/>
       <c r="E3" s="123"/>
       <c r="F3" s="123"/>
       <c r="G3" s="123"/>
@@ -3439,10 +3507,10 @@
       <c r="I3" s="123"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="154"/>
-      <c r="B4" s="154"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="159"/>
+      <c r="A4" s="150"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="155"/>
       <c r="E4" s="123"/>
       <c r="F4" s="123"/>
       <c r="G4" s="123"/>
@@ -3450,10 +3518,10 @@
       <c r="I4" s="123"/>
     </row>
     <row r="5" spans="1:48" ht="18.75" customHeight="1">
-      <c r="A5" s="155"/>
-      <c r="B5" s="155"/>
-      <c r="C5" s="157"/>
-      <c r="D5" s="159"/>
+      <c r="A5" s="151"/>
+      <c r="B5" s="151"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="155"/>
       <c r="E5" s="123"/>
       <c r="F5" s="123"/>
       <c r="G5" s="123"/>
@@ -3471,10 +3539,10 @@
       <c r="H6" s="119"/>
     </row>
     <row r="7" spans="1:48">
-      <c r="A7" s="150" t="s">
+      <c r="A7" s="146" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="150"/>
+      <c r="B7" s="146"/>
       <c r="C7" s="131"/>
       <c r="D7" s="131"/>
       <c r="E7" s="131"/>
@@ -3814,13 +3882,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="199" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="204"/>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
+      <c r="B1" s="200"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="200"/>
+      <c r="E1" s="200"/>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="61" t="s">
@@ -3862,13 +3930,13 @@
       <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="204" t="s">
+      <c r="A5" s="200" t="s">
         <v>311</v>
       </c>
-      <c r="B5" s="204"/>
-      <c r="C5" s="204"/>
-      <c r="D5" s="204"/>
-      <c r="E5" s="204"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="200"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="200"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="61" t="s">
@@ -4001,14 +4069,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="205" t="s">
+      <c r="A1" s="201" t="s">
         <v>318</v>
       </c>
-      <c r="B1" s="206"/>
-      <c r="C1" s="206"/>
-      <c r="D1" s="206"/>
-      <c r="E1" s="206"/>
-      <c r="F1" s="206"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
+      <c r="F1" s="202"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="66" t="s">
@@ -4017,10 +4085,10 @@
       <c r="B2" s="66" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="207" t="s">
+      <c r="C2" s="203" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="208"/>
+      <c r="D2" s="204"/>
       <c r="E2" s="66" t="s">
         <v>25</v>
       </c>
@@ -4035,8 +4103,8 @@
       <c r="B3" s="68" t="s">
         <v>319</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="210"/>
+      <c r="C3" s="205"/>
+      <c r="D3" s="206"/>
       <c r="E3" s="68" t="s">
         <v>29</v>
       </c>
@@ -4053,13 +4121,13 @@
       <c r="F4" s="69"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="206" t="s">
+      <c r="A5" s="202" t="s">
         <v>321</v>
       </c>
-      <c r="B5" s="206"/>
-      <c r="C5" s="206"/>
-      <c r="D5" s="206"/>
-      <c r="E5" s="206"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="202"/>
       <c r="F5" s="70"/>
     </row>
     <row r="6" spans="1:6">
@@ -5319,14 +5387,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="211" t="s">
+      <c r="A1" s="207" t="s">
         <v>387</v>
       </c>
-      <c r="B1" s="212"/>
-      <c r="C1" s="212"/>
-      <c r="D1" s="212"/>
-      <c r="E1" s="212"/>
-      <c r="F1" s="212"/>
+      <c r="B1" s="208"/>
+      <c r="C1" s="208"/>
+      <c r="D1" s="208"/>
+      <c r="E1" s="208"/>
+      <c r="F1" s="208"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="60" t="s">
@@ -5335,10 +5403,10 @@
       <c r="B2" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="212" t="s">
+      <c r="C2" s="208" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="212"/>
+      <c r="D2" s="208"/>
       <c r="E2" s="60" t="s">
         <v>25</v>
       </c>
@@ -5355,13 +5423,13 @@
       <c r="F3" s="75"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="212" t="s">
+      <c r="A4" s="208" t="s">
         <v>388</v>
       </c>
-      <c r="B4" s="212"/>
-      <c r="C4" s="212"/>
-      <c r="D4" s="212"/>
-      <c r="E4" s="212"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
       <c r="F4" s="76"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
@@ -6612,13 +6680,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A1" s="213" t="s">
+      <c r="A1" s="209" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="214"/>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="81" t="s">
@@ -6653,13 +6721,13 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="215" t="s">
+      <c r="A4" s="211" t="s">
         <v>393</v>
       </c>
-      <c r="B4" s="216"/>
-      <c r="C4" s="216"/>
-      <c r="D4" s="216"/>
-      <c r="E4" s="217"/>
+      <c r="B4" s="212"/>
+      <c r="C4" s="212"/>
+      <c r="D4" s="212"/>
+      <c r="E4" s="213"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="81" t="s">
@@ -6775,13 +6843,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="47.25" customHeight="1">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="214" t="s">
         <v>397</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
+      <c r="B1" s="215"/>
+      <c r="C1" s="215"/>
+      <c r="D1" s="215"/>
+      <c r="E1" s="215"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="85" t="s">
@@ -6808,13 +6876,13 @@
       <c r="E3" s="86"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="212" t="s">
+      <c r="A5" s="208" t="s">
         <v>398</v>
       </c>
-      <c r="B5" s="212"/>
-      <c r="C5" s="212"/>
-      <c r="D5" s="212"/>
-      <c r="E5" s="212"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="60" t="s">
@@ -7064,12 +7132,12 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6475A89-B7ED-43F3-BC39-CA3E8BE68933}">
-  <dimension ref="A1:F26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AED1B094-C16F-4630-9856-4FD81B0CAC3F}">
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="33"/>
-    <col min="2" max="2" width="42.5703125" style="33" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" style="33" customWidth="1"/>
     <col min="3" max="3" width="33.28515625" style="33" customWidth="1"/>
     <col min="4" max="4" width="10.7109375" style="33" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="84" customWidth="1"/>
@@ -7078,14 +7146,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="148"/>
-      <c r="C1" s="148"/>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="148"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
     </row>
     <row r="2" spans="1:6" ht="30.75">
       <c r="A2" s="137" t="s">
@@ -7120,10 +7188,10 @@
       <c r="D3" s="142" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="149" t="s">
+      <c r="E3" s="218" t="s">
         <v>408</v>
       </c>
-      <c r="F3" s="149"/>
+      <c r="F3" s="218"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="143"/>
@@ -7134,14 +7202,14 @@
       <c r="F4" s="143"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="147" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="148"/>
-      <c r="C5" s="148"/>
-      <c r="D5" s="148"/>
-      <c r="E5" s="148"/>
-      <c r="F5" s="148"/>
+      <c r="A5" s="216" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="217"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="137" t="s">
@@ -7196,11 +7264,11 @@
       <c r="D8" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E8" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F8" s="142" t="s">
-        <v>186</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7211,16 +7279,16 @@
         <v>410</v>
       </c>
       <c r="C9" s="142" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D9" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E9" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F9" s="142" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7231,19 +7299,19 @@
         <v>410</v>
       </c>
       <c r="C10" s="142" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D10" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E10" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F10" s="142" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="45.75">
       <c r="A11" s="141">
         <v>5</v>
       </c>
@@ -7251,19 +7319,19 @@
         <v>410</v>
       </c>
       <c r="C11" s="142" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D11" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E11" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E11" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F11" s="142" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="45.75">
       <c r="A12" s="141">
         <v>6</v>
       </c>
@@ -7271,19 +7339,19 @@
         <v>410</v>
       </c>
       <c r="C12" s="142" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D12" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E12" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E12" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F12" s="142" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30.75">
       <c r="A13" s="141">
         <v>7</v>
       </c>
@@ -7291,19 +7359,19 @@
         <v>410</v>
       </c>
       <c r="C13" s="142" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D13" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E13" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F13" s="142" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30.75">
       <c r="A14" s="141">
         <v>8</v>
       </c>
@@ -7311,19 +7379,19 @@
         <v>410</v>
       </c>
       <c r="C14" s="142" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D14" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E14" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E14" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F14" s="142" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="45.75">
       <c r="A15" s="141">
         <v>9</v>
       </c>
@@ -7331,19 +7399,19 @@
         <v>410</v>
       </c>
       <c r="C15" s="142" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D15" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E15" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F15" s="142" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30.75">
       <c r="A16" s="141">
         <v>10</v>
       </c>
@@ -7351,19 +7419,19 @@
         <v>410</v>
       </c>
       <c r="C16" s="142" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D16" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E16" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F16" s="142" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30.75">
       <c r="A17" s="141">
         <v>11</v>
       </c>
@@ -7371,16 +7439,16 @@
         <v>410</v>
       </c>
       <c r="C17" s="142" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D17" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E17" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F17" s="142" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7391,19 +7459,19 @@
         <v>410</v>
       </c>
       <c r="C18" s="142" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D18" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E18" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F18" s="142" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30.75">
       <c r="A19" s="141">
         <v>13</v>
       </c>
@@ -7411,19 +7479,19 @@
         <v>410</v>
       </c>
       <c r="C19" s="142" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D19" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E19" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F19" s="142" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30.75">
       <c r="A20" s="141">
         <v>14</v>
       </c>
@@ -7431,16 +7499,16 @@
         <v>410</v>
       </c>
       <c r="C20" s="142" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D20" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E20" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F20" s="142" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7451,16 +7519,16 @@
         <v>410</v>
       </c>
       <c r="C21" s="142" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D21" s="142" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E21" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F21" s="142" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7471,19 +7539,19 @@
         <v>410</v>
       </c>
       <c r="C22" s="142" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D22" s="142" t="s">
         <v>76</v>
       </c>
-      <c r="E22" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E22" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F22" s="142" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="45.75">
       <c r="A23" s="141">
         <v>17</v>
       </c>
@@ -7491,19 +7559,19 @@
         <v>410</v>
       </c>
       <c r="C23" s="142" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D23" s="142" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E23" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F23" s="142" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="45.75">
       <c r="A24" s="141">
         <v>18</v>
       </c>
@@ -7516,11 +7584,11 @@
       <c r="D24" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="E24" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E24" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F24" s="142" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7531,19 +7599,19 @@
         <v>410</v>
       </c>
       <c r="C25" s="142" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D25" s="142" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="146">
-        <v>4.2361111111111113E-2</v>
+      <c r="E25" s="145" t="s">
+        <v>226</v>
       </c>
       <c r="F25" s="142" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="91.5">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="60.75">
       <c r="A26" s="141">
         <v>20</v>
       </c>
@@ -7551,7 +7619,7 @@
         <v>410</v>
       </c>
       <c r="C26" s="142" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D26" s="142" t="s">
         <v>63</v>
@@ -7560,7 +7628,167 @@
         <v>226</v>
       </c>
       <c r="F26" s="142" t="s">
-        <v>447</v>
+        <v>448</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="45.75">
+      <c r="A27" s="141">
+        <v>21</v>
+      </c>
+      <c r="B27" s="142" t="s">
+        <v>410</v>
+      </c>
+      <c r="C27" s="142" t="s">
+        <v>449</v>
+      </c>
+      <c r="D27" s="142" t="s">
+        <v>63</v>
+      </c>
+      <c r="E27" s="145" t="s">
+        <v>450</v>
+      </c>
+      <c r="F27" s="142" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="45.75">
+      <c r="A28" s="141">
+        <v>22</v>
+      </c>
+      <c r="B28" s="142" t="s">
+        <v>410</v>
+      </c>
+      <c r="C28" s="142" t="s">
+        <v>452</v>
+      </c>
+      <c r="D28" s="142" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="145" t="s">
+        <v>450</v>
+      </c>
+      <c r="F28" s="142" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="45.75">
+      <c r="A29" s="141">
+        <v>23</v>
+      </c>
+      <c r="B29" s="142" t="s">
+        <v>410</v>
+      </c>
+      <c r="C29" s="142" t="s">
+        <v>454</v>
+      </c>
+      <c r="D29" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" s="145" t="s">
+        <v>450</v>
+      </c>
+      <c r="F29" s="142" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="45.75">
+      <c r="A30" s="141">
+        <v>24</v>
+      </c>
+      <c r="B30" s="142" t="s">
+        <v>410</v>
+      </c>
+      <c r="C30" s="142" t="s">
+        <v>456</v>
+      </c>
+      <c r="D30" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="E30" s="145" t="s">
+        <v>450</v>
+      </c>
+      <c r="F30" s="142" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="45.75">
+      <c r="A31" s="141">
+        <v>25</v>
+      </c>
+      <c r="B31" s="142" t="s">
+        <v>410</v>
+      </c>
+      <c r="C31" s="142" t="s">
+        <v>458</v>
+      </c>
+      <c r="D31" s="142" t="s">
+        <v>459</v>
+      </c>
+      <c r="E31" s="145" t="s">
+        <v>450</v>
+      </c>
+      <c r="F31" s="142" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="45.75">
+      <c r="A32" s="141">
+        <v>26</v>
+      </c>
+      <c r="B32" s="142" t="s">
+        <v>410</v>
+      </c>
+      <c r="C32" s="142" t="s">
+        <v>461</v>
+      </c>
+      <c r="D32" s="142" t="s">
+        <v>459</v>
+      </c>
+      <c r="E32" s="145" t="s">
+        <v>450</v>
+      </c>
+      <c r="F32" s="142" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="45.75">
+      <c r="A33" s="141">
+        <v>27</v>
+      </c>
+      <c r="B33" s="142" t="s">
+        <v>410</v>
+      </c>
+      <c r="C33" s="142" t="s">
+        <v>463</v>
+      </c>
+      <c r="D33" s="142" t="s">
+        <v>459</v>
+      </c>
+      <c r="E33" s="145" t="s">
+        <v>450</v>
+      </c>
+      <c r="F33" s="142" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="45.75">
+      <c r="A34" s="141">
+        <v>28</v>
+      </c>
+      <c r="B34" s="142" t="s">
+        <v>410</v>
+      </c>
+      <c r="C34" s="142" t="s">
+        <v>465</v>
+      </c>
+      <c r="D34" s="142" t="s">
+        <v>459</v>
+      </c>
+      <c r="E34" s="145" t="s">
+        <v>450</v>
+      </c>
+      <c r="F34" s="142" t="s">
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -7610,7 +7838,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.6">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -7618,7 +7846,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="33"/>
-      <c r="D3" s="220" t="s">
+      <c r="D3" s="219" t="s">
         <v>21</v>
       </c>
     </row>
@@ -7643,16 +7871,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="156" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="162"/>
-      <c r="H1" s="221"/>
+      <c r="B1" s="157"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
+      <c r="F1" s="157"/>
+      <c r="G1" s="158"/>
+      <c r="H1" s="220"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="93" t="s">
@@ -7667,12 +7895,12 @@
       <c r="D2" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="161" t="s">
+      <c r="E2" s="157" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="161"/>
-      <c r="G2" s="163"/>
-      <c r="H2" s="221"/>
+      <c r="F2" s="157"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="220"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="90">
@@ -7687,10 +7915,10 @@
       <c r="D3" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="165"/>
-      <c r="H3" s="221"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="220"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
       <c r="A4" s="90">
@@ -7705,24 +7933,24 @@
       <c r="D4" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="164" t="s">
+      <c r="E4" s="160" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="164"/>
-      <c r="G4" s="165"/>
-      <c r="H4" s="221"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="161"/>
+      <c r="H4" s="220"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="166" t="s">
+      <c r="A5" s="162" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="221"/>
+      <c r="B5" s="163"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="164"/>
+      <c r="H5" s="220"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="93" t="s">
@@ -7746,7 +7974,7 @@
       <c r="G6" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="221"/>
+      <c r="H6" s="220"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="90">
@@ -7770,7 +7998,7 @@
       <c r="G7" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="221"/>
+      <c r="H7" s="220"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="90">
@@ -7794,7 +8022,7 @@
       <c r="G8" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="221"/>
+      <c r="H8" s="220"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="90">
@@ -7818,7 +8046,7 @@
       <c r="G9" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="221"/>
+      <c r="H9" s="220"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="90">
@@ -7842,7 +8070,7 @@
       <c r="G10" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="221"/>
+      <c r="H10" s="220"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="90">
@@ -7866,7 +8094,7 @@
       <c r="G11" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H11" s="221"/>
+      <c r="H11" s="220"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="90">
@@ -7890,7 +8118,7 @@
       <c r="G12" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="221"/>
+      <c r="H12" s="220"/>
     </row>
     <row r="13" spans="1:8" ht="60.75">
       <c r="A13" s="90">
@@ -7914,7 +8142,7 @@
       <c r="G13" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="221"/>
+      <c r="H13" s="220"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="90">
@@ -7938,7 +8166,7 @@
       <c r="G14" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="221"/>
+      <c r="H14" s="220"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="90">
@@ -7962,7 +8190,7 @@
       <c r="G15" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="221"/>
+      <c r="H15" s="220"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="90">
@@ -7986,7 +8214,7 @@
       <c r="G16" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="221"/>
+      <c r="H16" s="220"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="90">
@@ -8010,7 +8238,7 @@
       <c r="G17" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="221"/>
+      <c r="H17" s="220"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="90">
@@ -8034,7 +8262,7 @@
       <c r="G18" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H18" s="221"/>
+      <c r="H18" s="220"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="90">
@@ -8058,7 +8286,7 @@
       <c r="G19" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="221"/>
+      <c r="H19" s="220"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="90">
@@ -8082,7 +8310,7 @@
       <c r="G20" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H20" s="221"/>
+      <c r="H20" s="220"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="90">
@@ -8106,7 +8334,7 @@
       <c r="G21" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="221"/>
+      <c r="H21" s="220"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="90">
@@ -8130,7 +8358,7 @@
       <c r="G22" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H22" s="221"/>
+      <c r="H22" s="220"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="90">
@@ -8154,7 +8382,7 @@
       <c r="G23" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="221"/>
+      <c r="H23" s="220"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="90">
@@ -8178,7 +8406,7 @@
       <c r="G24" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="221"/>
+      <c r="H24" s="220"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="90">
@@ -8202,7 +8430,7 @@
       <c r="G25" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H25" s="221"/>
+      <c r="H25" s="220"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="90">
@@ -8226,7 +8454,7 @@
       <c r="G26" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H26" s="221"/>
+      <c r="H26" s="220"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="90">
@@ -8250,7 +8478,7 @@
       <c r="G27" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H27" s="221"/>
+      <c r="H27" s="220"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="90">
@@ -8274,7 +8502,7 @@
       <c r="G28" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H28" s="221"/>
+      <c r="H28" s="220"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="90">
@@ -8298,7 +8526,7 @@
       <c r="G29" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H29" s="221"/>
+      <c r="H29" s="220"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="90">
@@ -8322,7 +8550,7 @@
       <c r="G30" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H30" s="221"/>
+      <c r="H30" s="220"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="90">
@@ -8346,7 +8574,7 @@
       <c r="G31" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H31" s="221"/>
+      <c r="H31" s="220"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="90">
@@ -8370,7 +8598,7 @@
       <c r="G32" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H32" s="221"/>
+      <c r="H32" s="220"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="90">
@@ -8394,7 +8622,7 @@
       <c r="G33" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H33" s="221"/>
+      <c r="H33" s="220"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="90">
@@ -8418,7 +8646,7 @@
       <c r="G34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H34" s="221"/>
+      <c r="H34" s="220"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="90">
@@ -8442,7 +8670,7 @@
       <c r="G35" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H35" s="221"/>
+      <c r="H35" s="220"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="90">
@@ -8466,7 +8694,7 @@
       <c r="G36" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H36" s="221"/>
+      <c r="H36" s="220"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="90">
@@ -8490,7 +8718,7 @@
       <c r="G37" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H37" s="221"/>
+      <c r="H37" s="220"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="90">
@@ -8514,7 +8742,7 @@
       <c r="G38" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H38" s="221"/>
+      <c r="H38" s="220"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="90">
@@ -8538,7 +8766,7 @@
       <c r="G39" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H39" s="221"/>
+      <c r="H39" s="220"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="90">
@@ -8562,7 +8790,7 @@
       <c r="G40" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H40" s="221"/>
+      <c r="H40" s="220"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="90">
@@ -8586,7 +8814,7 @@
       <c r="G41" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H41" s="221"/>
+      <c r="H41" s="220"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="90">
@@ -8610,7 +8838,7 @@
       <c r="G42" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H42" s="221"/>
+      <c r="H42" s="220"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="90">
@@ -8634,7 +8862,7 @@
       <c r="G43" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H43" s="221"/>
+      <c r="H43" s="220"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="90">
@@ -8658,7 +8886,7 @@
       <c r="G44" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H44" s="221"/>
+      <c r="H44" s="220"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="90">
@@ -8682,7 +8910,7 @@
       <c r="G45" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H45" s="221"/>
+      <c r="H45" s="220"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="90">
@@ -8706,7 +8934,7 @@
       <c r="G46" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H46" s="221"/>
+      <c r="H46" s="220"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="90">
@@ -8730,7 +8958,7 @@
       <c r="G47" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H47" s="221"/>
+      <c r="H47" s="220"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="90">
@@ -8754,7 +8982,7 @@
       <c r="G48" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H48" s="221"/>
+      <c r="H48" s="220"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="90">
@@ -8778,7 +9006,7 @@
       <c r="G49" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H49" s="221"/>
+      <c r="H49" s="220"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="90">
@@ -8802,7 +9030,7 @@
       <c r="G50" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H50" s="221"/>
+      <c r="H50" s="220"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="90">
@@ -8826,7 +9054,7 @@
       <c r="G51" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H51" s="221"/>
+      <c r="H51" s="220"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="90">
@@ -8850,7 +9078,7 @@
       <c r="G52" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H52" s="221"/>
+      <c r="H52" s="220"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="90">
@@ -8874,7 +9102,7 @@
       <c r="G53" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H53" s="221"/>
+      <c r="H53" s="220"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="90">
@@ -8898,7 +9126,7 @@
       <c r="G54" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H54" s="221"/>
+      <c r="H54" s="220"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="90">
@@ -8922,7 +9150,7 @@
       <c r="G55" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H55" s="221"/>
+      <c r="H55" s="220"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="90">
@@ -8946,7 +9174,7 @@
       <c r="G56" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H56" s="221"/>
+      <c r="H56" s="220"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="90">
@@ -8970,7 +9198,7 @@
       <c r="G57" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H57" s="221"/>
+      <c r="H57" s="220"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="114">
@@ -8994,137 +9222,137 @@
       <c r="G58" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H58" s="221"/>
+      <c r="H58" s="220"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="222">
+      <c r="A59" s="221">
         <v>53</v>
       </c>
-      <c r="B59" s="223" t="s">
+      <c r="B59" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="224" t="s">
+      <c r="C59" s="223" t="s">
         <v>154</v>
       </c>
-      <c r="D59" s="225" t="s">
+      <c r="D59" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="E59" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="223" t="s">
+      <c r="E59" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="222" t="s">
         <v>155</v>
       </c>
-      <c r="G59" s="223" t="s">
+      <c r="G59" s="222" t="s">
         <v>46</v>
       </c>
-      <c r="H59" s="221"/>
+      <c r="H59" s="220"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="222">
+      <c r="A60" s="221">
         <v>54</v>
       </c>
-      <c r="B60" s="223" t="s">
+      <c r="B60" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C60" s="224" t="s">
+      <c r="C60" s="223" t="s">
         <v>156</v>
       </c>
-      <c r="D60" s="225" t="s">
+      <c r="D60" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="E60" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F60" s="223" t="s">
+      <c r="E60" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F60" s="222" t="s">
         <v>157</v>
       </c>
-      <c r="G60" s="223" t="s">
+      <c r="G60" s="222" t="s">
         <v>46</v>
       </c>
-      <c r="H60" s="221"/>
+      <c r="H60" s="220"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="222">
+      <c r="A61" s="221">
         <v>55</v>
       </c>
-      <c r="B61" s="223" t="s">
+      <c r="B61" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C61" s="224" t="s">
+      <c r="C61" s="223" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="225" t="s">
+      <c r="D61" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="E61" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F61" s="223" t="s">
+      <c r="E61" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" s="222" t="s">
         <v>159</v>
       </c>
-      <c r="G61" s="223" t="s">
+      <c r="G61" s="222" t="s">
         <v>46</v>
       </c>
-      <c r="H61" s="221"/>
+      <c r="H61" s="220"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="222">
+      <c r="A62" s="221">
         <v>56</v>
       </c>
-      <c r="B62" s="223" t="s">
+      <c r="B62" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C62" s="224" t="s">
+      <c r="C62" s="223" t="s">
         <v>160</v>
       </c>
-      <c r="D62" s="225" t="s">
+      <c r="D62" s="224" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F62" s="223" t="s">
+      <c r="E62" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" s="222" t="s">
         <v>161</v>
       </c>
-      <c r="G62" s="223" t="s">
+      <c r="G62" s="222" t="s">
         <v>46</v>
       </c>
-      <c r="H62" s="221"/>
+      <c r="H62" s="220"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="222">
+      <c r="A63" s="221">
         <v>57</v>
       </c>
-      <c r="B63" s="223" t="s">
+      <c r="B63" s="222" t="s">
         <v>41</v>
       </c>
-      <c r="C63" s="224" t="s">
+      <c r="C63" s="223" t="s">
         <v>162</v>
       </c>
-      <c r="D63" s="225" t="s">
+      <c r="D63" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="E63" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F63" s="223" t="s">
+      <c r="E63" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F63" s="222" t="s">
         <v>163</v>
       </c>
-      <c r="G63" s="223" t="s">
+      <c r="G63" s="222" t="s">
         <v>46</v>
       </c>
-      <c r="H63" s="221"/>
+      <c r="H63" s="220"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="227"/>
-      <c r="B64" s="221"/>
-      <c r="C64" s="227"/>
-      <c r="D64" s="227"/>
-      <c r="E64" s="221"/>
-      <c r="F64" s="221"/>
-      <c r="G64" s="221"/>
-      <c r="H64" s="228"/>
+      <c r="A64" s="226"/>
+      <c r="B64" s="220"/>
+      <c r="C64" s="226"/>
+      <c r="D64" s="226"/>
+      <c r="E64" s="220"/>
+      <c r="F64" s="220"/>
+      <c r="G64" s="220"/>
+      <c r="H64" s="227"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9152,14 +9380,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="165" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -9169,10 +9397,10 @@
       <c r="B2" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="171" t="s">
+      <c r="C2" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="172"/>
+      <c r="D2" s="168"/>
       <c r="E2" s="40" t="s">
         <v>25</v>
       </c>
@@ -9188,10 +9416,10 @@
       <c r="B3" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="173" t="s">
+      <c r="C3" s="169" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="174"/>
+      <c r="D3" s="170"/>
       <c r="E3" s="41" t="s">
         <v>29</v>
       </c>
@@ -9207,10 +9435,10 @@
       <c r="B4" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="173" t="s">
+      <c r="C4" s="169" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="174"/>
+      <c r="D4" s="170"/>
       <c r="E4" s="41" t="s">
         <v>32</v>
       </c>
@@ -9219,14 +9447,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="170" t="s">
+      <c r="A5" s="166" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="170"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="170"/>
-      <c r="F5" s="170"/>
+      <c r="B5" s="166"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="166"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="40" t="s">
@@ -9356,14 +9584,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="175" t="s">
+      <c r="A1" s="171" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="172"/>
+      <c r="F1" s="172"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="46" t="s">
@@ -9372,10 +9600,10 @@
       <c r="B2" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="177" t="s">
+      <c r="C2" s="173" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="178"/>
+      <c r="D2" s="174"/>
       <c r="E2" s="46" t="s">
         <v>25</v>
       </c>
@@ -9390,10 +9618,10 @@
       <c r="B3" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="179" t="s">
+      <c r="C3" s="175" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="180"/>
+      <c r="D3" s="176"/>
       <c r="E3" s="47" t="s">
         <v>29</v>
       </c>
@@ -9406,10 +9634,10 @@
       <c r="B4" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="181" t="s">
+      <c r="C4" s="177" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="182"/>
+      <c r="D4" s="178"/>
       <c r="E4" s="49" t="s">
         <v>191</v>
       </c>
@@ -9418,22 +9646,22 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A5" s="228"/>
-      <c r="B5" s="228"/>
-      <c r="C5" s="228"/>
-      <c r="D5" s="228"/>
-      <c r="E5" s="228"/>
-      <c r="F5" s="228"/>
+      <c r="A5" s="227"/>
+      <c r="B5" s="227"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="177" t="s">
+      <c r="A7" s="173" t="s">
         <v>193</v>
       </c>
-      <c r="B7" s="183"/>
-      <c r="C7" s="183"/>
-      <c r="D7" s="183"/>
-      <c r="E7" s="183"/>
-      <c r="F7" s="228"/>
+      <c r="B7" s="179"/>
+      <c r="C7" s="179"/>
+      <c r="D7" s="179"/>
+      <c r="E7" s="179"/>
+      <c r="F7" s="227"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="46" t="s">
@@ -9451,7 +9679,7 @@
       <c r="E8" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="228"/>
+      <c r="F8" s="227"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="51" t="s">
@@ -9469,7 +9697,7 @@
       <c r="E9" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="F9" s="228"/>
+      <c r="F9" s="227"/>
     </row>
     <row r="10" spans="1:6" ht="60.75">
       <c r="A10" s="51" t="s">
@@ -9487,7 +9715,7 @@
       <c r="E10" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F10" s="228"/>
+      <c r="F10" s="227"/>
     </row>
     <row r="11" spans="1:6" ht="91.5">
       <c r="A11" s="51" t="s">
@@ -9505,7 +9733,7 @@
       <c r="E11" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="F11" s="228"/>
+      <c r="F11" s="227"/>
     </row>
     <row r="12" spans="1:6" ht="121.5">
       <c r="A12" s="51" t="s">
@@ -9523,7 +9751,7 @@
       <c r="E12" s="54" t="s">
         <v>203</v>
       </c>
-      <c r="F12" s="228"/>
+      <c r="F12" s="227"/>
     </row>
     <row r="13" spans="1:6" ht="76.5">
       <c r="A13" s="51" t="s">
@@ -9541,7 +9769,7 @@
       <c r="E13" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="F13" s="228"/>
+      <c r="F13" s="227"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="51" t="s">
@@ -9559,7 +9787,7 @@
       <c r="E14" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="F14" s="228"/>
+      <c r="F14" s="227"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="51" t="s">
@@ -9577,7 +9805,7 @@
       <c r="E15" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="F15" s="228"/>
+      <c r="F15" s="227"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9604,13 +9832,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="186" t="s">
+      <c r="A1" s="182" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="187"/>
-      <c r="C1" s="187"/>
-      <c r="D1" s="187"/>
-      <c r="E1" s="188"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="184"/>
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
@@ -9711,39 +9939,39 @@
       <c r="E7" s="30"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="186" t="s">
+      <c r="A8" s="182" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="187"/>
-      <c r="C8" s="187"/>
-      <c r="D8" s="187"/>
-      <c r="E8" s="187"/>
+      <c r="B8" s="183"/>
+      <c r="C8" s="183"/>
+      <c r="D8" s="183"/>
+      <c r="E8" s="183"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="189" t="s">
+      <c r="A9" s="185" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="190" t="s">
+      <c r="B9" s="186" t="s">
         <v>222</v>
       </c>
-      <c r="C9" s="190" t="s">
+      <c r="C9" s="186" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="191" t="s">
+      <c r="D9" s="187" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="191" t="s">
+      <c r="E9" s="187" t="s">
         <v>223</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="189"/>
-      <c r="B10" s="190"/>
-      <c r="C10" s="190"/>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
+      <c r="A10" s="185"/>
+      <c r="B10" s="186"/>
+      <c r="C10" s="186"/>
+      <c r="D10" s="188"/>
+      <c r="E10" s="188"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6">
@@ -10773,13 +11001,13 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="184" t="s">
+      <c r="A68" s="180" t="s">
         <v>240</v>
       </c>
-      <c r="B68" s="185"/>
-      <c r="C68" s="185"/>
-      <c r="D68" s="185"/>
-      <c r="E68" s="185"/>
+      <c r="B68" s="181"/>
+      <c r="C68" s="181"/>
+      <c r="D68" s="181"/>
+      <c r="E68" s="181"/>
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
@@ -11828,13 +12056,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="189" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="194"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="195"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="191"/>
       <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6">
@@ -11881,13 +12109,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="196" t="s">
+      <c r="A5" s="192" t="s">
         <v>272</v>
       </c>
-      <c r="B5" s="196"/>
-      <c r="C5" s="196"/>
-      <c r="D5" s="196"/>
-      <c r="E5" s="196"/>
+      <c r="B5" s="192"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="192"/>
       <c r="F5" s="106"/>
     </row>
     <row r="6" spans="1:6">
@@ -12070,13 +12298,13 @@
       <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="197" t="s">
+      <c r="A5" s="193" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="197"/>
-      <c r="C5" s="197"/>
-      <c r="D5" s="197"/>
-      <c r="E5" s="197"/>
+      <c r="B5" s="193"/>
+      <c r="C5" s="193"/>
+      <c r="D5" s="193"/>
+      <c r="E5" s="193"/>
     </row>
     <row r="6" spans="1:5" ht="24.75">
       <c r="A6" s="21" t="s">
@@ -12264,8 +12492,8 @@
       </c>
       <c r="B6" s="58"/>
       <c r="C6" s="58"/>
-      <c r="D6" s="200"/>
-      <c r="E6" s="200"/>
+      <c r="D6" s="196"/>
+      <c r="E6" s="196"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
@@ -12278,10 +12506,10 @@
       <c r="C7" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="201" t="s">
+      <c r="D7" s="197" t="s">
         <v>174</v>
       </c>
-      <c r="E7" s="202"/>
+      <c r="E7" s="198"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
@@ -12294,10 +12522,10 @@
       <c r="C8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="198" t="s">
+      <c r="D8" s="194" t="s">
         <v>298</v>
       </c>
-      <c r="E8" s="199"/>
+      <c r="E8" s="195"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1">
@@ -12310,10 +12538,10 @@
       <c r="C9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="198" t="s">
+      <c r="D9" s="194" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="199"/>
+      <c r="E9" s="195"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
@@ -12326,10 +12554,10 @@
       <c r="C10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="198" t="s">
+      <c r="D10" s="194" t="s">
         <v>96</v>
       </c>
-      <c r="E10" s="199"/>
+      <c r="E10" s="195"/>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="8" t="s">
@@ -12341,10 +12569,10 @@
       <c r="C11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="198" t="s">
+      <c r="D11" s="194" t="s">
         <v>98</v>
       </c>
-      <c r="E11" s="199"/>
+      <c r="E11" s="195"/>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="8" t="s">
@@ -12356,10 +12584,10 @@
       <c r="C12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="198" t="s">
+      <c r="D12" s="194" t="s">
         <v>300</v>
       </c>
-      <c r="E12" s="199"/>
+      <c r="E12" s="195"/>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="8" t="s">
@@ -12371,10 +12599,10 @@
       <c r="C13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="198" t="s">
+      <c r="D13" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="199"/>
+      <c r="E13" s="195"/>
     </row>
     <row r="14" spans="1:7" ht="70.5" customHeight="1">
       <c r="A14" s="8" t="s">
@@ -12386,10 +12614,10 @@
       <c r="C14" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="198" t="s">
+      <c r="D14" s="194" t="s">
         <v>302</v>
       </c>
-      <c r="E14" s="199"/>
+      <c r="E14" s="195"/>
     </row>
     <row r="15" spans="1:7" ht="14.45" customHeight="1"/>
   </sheetData>
@@ -12409,25 +12637,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -12599,14 +12808,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74B1DDD3-2176-4CA0-892E-905566AB1E8D}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>